--- a/feedback_surveys/020_resource_allocation_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/020_resource_allocation_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>resource_allocation_survey</t>
+          <t>resources_access</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your role in the organization?</t>
+          <t>How many resources do you currently have access to?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>hours_available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>How many hours do you have available per week?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>allocated_resources</t>
+          <t>resource_distribution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How many resources do you currently have access to?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please enter a number</t>
-        </is>
-      </c>
+          <t>Do you think resource distribution is working well?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>allocated_resources_amount</t>
+          <t>resource_availability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How many hours do you have available?</t>
+          <t>Can you access all necessary resources?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,24 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>resource_distribution</t>
+          <t>additional_resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Do you think resource distribution is working well?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Please select one option</t>
-        </is>
-      </c>
+          <t>Are there any additional resources you'd like to request?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -638,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>resource_availability</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Can you access all necessary resources?</t>
+          <t>What is your role in the organization?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -666,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>additional_resources</t>
+          <t>thoughts_on_resource_distribution</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Is there anything else you'd like to add?</t>
+          <t>What are your thoughts on resource distribution?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -684,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>available_hours_use</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>How do you currently use your available hours?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>skills_to_perform_job</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Do you feel you have the necessary skills to perform your job?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>resource_accessing_challenges</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What are some challenges you face when accessing resources?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>improve_resource_distribution</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>How do you think resource distribution could be improved?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,336 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Are there any other comments or suggestions you'd like to share?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>resource_availability_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Is there anything else you'd like to add?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>resource_distribution_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Do you think resource distribution is working well?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Please select one option</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>resource_availability_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Can you access all necessary resources?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>resource_distribution_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Do you think resource distribution is working well?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Please select one option</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>allocated_resources_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How many resources do you currently have access to?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Please enter a number</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>allocated_resources_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How many hours do you have available?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>resource_distribution_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Do you think resource distribution is working well?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Please select one option</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>resource_availability_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Can you access all necessary resources?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>allocated_resources_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Is there anything else you'd like to add?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>resource_allocation_survey_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Resource allocation survey 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>resource_availability_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Can you access all necessary resources?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>resource_distribution_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you think resource distribution is working well?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>resource_allocation_survey_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Resource allocation survey 3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1150,194 +827,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>resource_allocation_survey_choices</t>
+          <t>resources_access_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>resource_allocation_survey_choices</t>
+          <t>resources_access_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>resources_access_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>11-15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>resources_access_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>more_than_15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>More than 15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>resource_distribution_choices</t>
+          <t>hours_available_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_10_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 10 hours</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>resource_distribution_choices</t>
+          <t>hours_available_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>10-20_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>10-20 hours</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>resource_distribution_choices</t>
+          <t>hours_available_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>21-30_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Undecided</t>
+          <t>21-30 hours</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>resource_availability_choices</t>
+          <t>hours_available_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>more_than_30_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>More than 30 hours</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>resource_availability_choices</t>
+          <t>resource_distribution_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>resource_availability_2_choices</t>
+          <t>resource_distribution_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>resource_availability_2_choices</t>
+          <t>resource_distribution_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>resource_distribution_2_choices</t>
+          <t>resource_availability_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1354,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>resource_distribution_2_choices</t>
+          <t>resource_availability_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1371,270 +1048,151 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>resource_availability_3_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>team_leader</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Team leader</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>resource_availability_3_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Team member</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>resource_distribution_3_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>resource_distribution_3_choices</t>
+          <t>available_hours_use_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>working_on_core_tasks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Working on core tasks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>resource_distribution_4_choices</t>
+          <t>available_hours_use_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>collaborating_with_team_members</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Collaborating with team members</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>resource_distribution_4_choices</t>
+          <t>available_hours_use_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>learning/professional_development</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Learning/Professional development</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>resource_availability_4_choices</t>
+          <t>available_hours_use_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>resource_availability_4_choices</t>
+          <t>skills_to_perform_job_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>resource_allocation_survey_2_choices</t>
+          <t>skills_to_perform_job_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>resource_allocation_survey_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>resource_availability_5_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>resource_availability_5_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>resource_distribution_5_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>resource_distribution_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>resource_allocation_survey_3_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>resource_allocation_survey_3_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
